--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.85594828904763</v>
+        <v>10.05159159697024</v>
       </c>
       <c r="D2" t="n">
-        <v>44.48981041066669</v>
+        <v>7.229594191733337</v>
       </c>
       <c r="E2" t="n">
-        <v>16.96617344527906</v>
+        <v>2.757003184857848</v>
       </c>
       <c r="F2" t="n">
-        <v>8.160457712312757</v>
+        <v>1.326074378250823</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.78429837487605</v>
+        <v>3.052448485917358</v>
       </c>
       <c r="D3" t="n">
-        <v>30.82053800471692</v>
+        <v>5.008337425766499</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96617344527906</v>
+        <v>2.757003184857848</v>
       </c>
       <c r="F3" t="n">
-        <v>8.160457712312757</v>
+        <v>1.326074378250823</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.22841570624378</v>
+        <v>5.399617552264615</v>
       </c>
       <c r="D4" t="n">
-        <v>34.32676680160857</v>
+        <v>5.578099605261393</v>
       </c>
       <c r="E4" t="n">
-        <v>16.96617344527906</v>
+        <v>2.757003184857848</v>
       </c>
       <c r="F4" t="n">
-        <v>8.160457712312757</v>
+        <v>1.326074378250823</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.02752798029003</v>
+        <v>3.57947329679713</v>
       </c>
       <c r="D5" t="n">
-        <v>21.68805852608678</v>
+        <v>3.524309510489103</v>
       </c>
       <c r="E5" t="n">
-        <v>16.96617344527906</v>
+        <v>2.757003184857848</v>
       </c>
       <c r="F5" t="n">
-        <v>8.160457712312757</v>
+        <v>1.326074378250823</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
